--- a/companies/openai/financials/openai_model_2026-08-14.xlsx
+++ b/companies/openai/financials/openai_model_2026-08-14.xlsx
@@ -1418,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J21"/>
+  <dimension ref="B2:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1584,16 +1584,16 @@
     <row r="10">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Total raised (equity and debt)</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr"/>
       <c r="D10" s="29" t="n">
-        <v>186.4</v>
+        <v>86</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1603,23 +1603,23 @@
       </c>
       <c r="J10" s="28" t="inlineStr">
         <is>
-          <t>PitchBook $186.4365B</t>
+          <t>PitchBook deal 248325-58T (Secondary Transaction - Private)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Equity raised</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr"/>
       <c r="D11" s="29" t="n">
-        <v>181.2</v>
+        <v>157</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1629,23 +1629,23 @@
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>canonical: excludes $5.2365B debt (incl. $520M Jul-8 deal 338367-43T)</t>
+          <t>PitchBook deal 243849-70T (Later Stage VC)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Debt raised</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr"/>
       <c r="D12" s="29" t="n">
-        <v>5.2</v>
+        <v>157</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1655,129 +1655,127 @@
       </c>
       <c r="J12" s="28" t="inlineStr">
         <is>
-          <t>PitchBook debt decomposition</t>
+          <t>PitchBook deal 297374-23T (Secondary Transaction - Private)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Annualised revenue</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr"/>
       <c r="D13" s="29" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="J13" s="28" t="inlineStr">
         <is>
-          <t>desk estimate, net basis</t>
+          <t>PitchBook deal 278597-80T (Later Stage VC)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Fy2025 leak</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Rev $13.07B / op loss $20.92B / group loss $60.35B incl. $41</t>
-        </is>
+      <c r="D14" s="29" t="n">
+        <v>500</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="J14" s="28" t="inlineStr">
         <is>
-          <t>press reports of audited FY2025 (verified leak)</t>
+          <t>PitchBook deal 308864-98T (Secondary Transaction - Private)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Gross margin 2025 (%)</t>
+          <t>Valuation history</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr"/>
       <c r="D15" s="29" t="n">
-        <v>33</v>
+        <v>852</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="J15" s="28" t="inlineStr">
         <is>
-          <t>investor documents (press-reported)</t>
+          <t>PitchBook deal 320989-60T (Later Stage VC)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Infra obligations tn</t>
+          <t>Total raised (equity and debt)</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr"/>
       <c r="D16" s="29" t="n">
-        <v>1.15</v>
+        <v>186.4</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="J16" s="28" t="inlineStr">
         <is>
-          <t>investor documents (press-reported), 7 vendors</t>
+          <t>PitchBook $186.4365B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>Equity raised</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr"/>
       <c r="D17" s="29" t="n">
-        <v>4500</v>
+        <v>181.2</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -1787,21 +1785,19 @@
       </c>
       <c r="J17" s="28" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>canonical: excludes $5.2365B debt (incl. $520M Jul-8 deal 338367-43T)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Altman pb listing</t>
+          <t>Debt raised</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr"/>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>PB lists Altman as 'Co-Founder, Co-CEO &amp; Board Member', pers</t>
-        </is>
+      <c r="D18" s="29" t="n">
+        <v>5.2</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -1815,25 +1811,25 @@
       </c>
       <c r="J18" s="28" t="inlineStr">
         <is>
-          <t>PitchBook profile</t>
+          <t>PitchBook debt decomposition</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>IPO filing status</t>
+          <t>Last completed round</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr"/>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Confidential S-1 filed Jun 8, 2026</t>
+          <t>Debt - General $520M (round n/a)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -1843,25 +1839,23 @@
       </c>
       <c r="J19" s="28" t="inlineStr">
         <is>
-          <t>press + PitchBook</t>
+          <t>PitchBook deal 338367-43T</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Expected IPO window</t>
+          <t>Raised to date ($bn)</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr"/>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>September 2026 (PitchBook, note refreshed Jul 9) vs media 20</t>
-        </is>
+      <c r="D20" s="29" t="n">
+        <v>186.436</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -1871,31 +1865,275 @@
       </c>
       <c r="J20" s="28" t="inlineStr">
         <is>
-          <t>PitchBook + press</t>
+          <t>PitchBook Raised to Date, deal 338367-43T</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="17" t="inlineStr">
         <is>
+          <t>Deal history</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr"/>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>2024-09-30 Secondary Transaction - Private; 2024-10-02 Later</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
+        <is>
+          <t>PitchBook deal history</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Annualised revenue</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr"/>
+      <c r="D22" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="inlineStr">
+        <is>
+          <t>desk estimate, net basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Fy2025 leak</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr"/>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Rev $13.07B / op loss $20.92B / group loss $60.35B incl. $41</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="inlineStr">
+        <is>
+          <t>press reports of audited FY2025 (verified leak)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Gross margin 2025 (%)</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr"/>
+      <c r="D24" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="J24" s="28" t="inlineStr">
+        <is>
+          <t>investor documents (press-reported)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Infra obligations tn</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr"/>
+      <c r="D25" s="29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="inlineStr">
+        <is>
+          <t>investor documents (press-reported), 7 vendors</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr"/>
+      <c r="D26" s="29" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J26" s="28" t="inlineStr">
+        <is>
+          <t>PitchBook</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Altman pb listing</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr"/>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>PB lists Altman as 'Co-Founder, Co-CEO &amp; Board Member', pers</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J27" s="28" t="inlineStr">
+        <is>
+          <t>PitchBook profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>IPO filing status</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr"/>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Confidential S-1 filed Jun 8, 2026</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J28" s="28" t="inlineStr">
+        <is>
+          <t>press + PitchBook</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Expected IPO window</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr"/>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>September 2026 (PitchBook, note refreshed Jul 9) vs media 20</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="J29" s="28" t="inlineStr">
+        <is>
+          <t>PitchBook + press</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="17" t="inlineStr">
+        <is>
           <t>Quality score (composite)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr"/>
-      <c r="D21" s="29" t="n">
+      <c r="C30" s="17" t="inlineStr"/>
+      <c r="D30" s="29" t="n">
         <v>4.53</v>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J30" s="28" t="inlineStr">
         <is>
           <t>internal AIBQ v3.0 (this desk)</t>
         </is>
